--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486742_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486742_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3666</v>
+        <v>0.4746</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.138</v>
+        <v>-1.7513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5047</v>
+        <v>2.2259</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0692</v>
+        <v>-3.2162</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6208</v>
+        <v>-2.269</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5516</v>
+        <v>-0.9472</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6895</v>
+        <v>-1.7321</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6895</v>
+        <v>-0.889</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.8431</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6203</v>
+        <v>-1.4841</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0687</v>
+        <v>-1.3801</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5516</v>
+        <v>-0.1041</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.4754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4358</v>
+        <v>-1.1518</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5515</v>
+        <v>-1.1384</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1156</v>
+        <v>-0.0134</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.3326</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.0845</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1666</v>
+        <v>0.2136</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.2684</v>
+        <v>-1.1752</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1018</v>
+        <v>1.3888</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.2162</v>
+        <v>-0.5283</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.269</v>
+        <v>-1.1659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9472</v>
+        <v>0.6375</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.7321</v>
+        <v>1.5698</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.889</v>
+        <v>1.1107</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8431</v>
+        <v>0.4591</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4841</v>
+        <v>-2.0981</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3801</v>
+        <v>-2.2766</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1041</v>
+        <v>0.1785</v>
       </c>
       <c r="P3" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4754</v>
+        <v>3.0892</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7931</v>
+        <v>-0.7448</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6555</v>
+        <v>-0.8142</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1376</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3326</v>
+        <v>0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0845</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2481</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1864</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0842</v>
+        <v>0.0193</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1022</v>
+        <v>-0.0277</v>
       </c>
       <c r="G4" t="n">
         <v>0.1501</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3365</v>
+        <v>-0.1586</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3821</v>
+        <v>-0.2209</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7957</v>
+        <v>-0.5517</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4136</v>
+        <v>0.3308</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5283</v>
+        <v>-0.0692</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1659</v>
+        <v>-0.6208</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6375</v>
+        <v>0.5516</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5698</v>
+        <v>-0.6895</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1107</v>
+        <v>-0.6895</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4591</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0981</v>
+        <v>0.6203</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2766</v>
+        <v>0.0687</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1785</v>
+        <v>0.5516</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0892</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3405</v>
+        <v>-0.1517</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4347</v>
+        <v>0.1378</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.2895</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5327</v>
+        <v>-0.6554</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5987</v>
+        <v>-0.0414</v>
       </c>
       <c r="F6" t="n">
-        <v>2.066</v>
+        <v>-0.6139</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.2651</v>
+        <v>-0.7312</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.0818</v>
+        <v>-0.6001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8167</v>
+        <v>-0.1311</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8495</v>
+        <v>0.0207</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.805</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9555</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4156</v>
+        <v>-0.7519</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2768</v>
+        <v>-0.6208</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8612</v>
+        <v>-0.1311</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3169</v>
+        <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2823</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6895</v>
+        <v>-0.1172</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2971</v>
+        <v>-0.0621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6076</v>
+        <v>-0.0551</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1049</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7208</v>
+        <v>-1.1328</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6331</v>
+        <v>-2.7021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9123</v>
+        <v>1.5693</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7257</v>
+        <v>-3.2651</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1447</v>
+        <v>-6.0818</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5809</v>
+        <v>2.8167</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.8007</v>
+        <v>-1.8495</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3856</v>
+        <v>-3.805</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4151</v>
+        <v>1.9555</v>
       </c>
       <c r="M7" t="n">
-        <v>0.075</v>
+        <v>-1.4156</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7591</v>
+        <v>-2.2768</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8341</v>
+        <v>0.8612</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5446</v>
+        <v>3.2823</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2628</v>
+        <v>-1.2895</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8474</v>
+        <v>-1.4005</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5846</v>
+        <v>0.111</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1628</v>
+        <v>1.1049</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1228</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8085</v>
+        <v>-1.9701</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1449</v>
+        <v>-3.081</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6636</v>
+        <v>1.1109</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7312</v>
+        <v>-2.7257</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6001</v>
+        <v>-2.1447</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1311</v>
+        <v>-0.5809</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0207</v>
+        <v>-2.8007</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>-1.3856</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.4151</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7519</v>
+        <v>0.075</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6208</v>
+        <v>-0.7591</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1311</v>
+        <v>0.8341</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2703</v>
+        <v>0.0135</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1655</v>
+        <v>0.3994</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1048</v>
+        <v>-0.3859</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2043</v>
+        <v>-2.254</v>
       </c>
       <c r="E9" t="n">
         <v>-1.2599</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9444</v>
+        <v>-0.9941</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4844</v>
@@ -1156,13 +1156,13 @@
         <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3806</v>
+        <v>0.3309</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3809</v>
+        <v>0.3313</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0814</v>
+        <v>-2.3714</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9032</v>
+        <v>-1.6191</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1782</v>
+        <v>-0.7523</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1377</v>
+        <v>-3.8648</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1381</v>
+        <v>-2.4066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2758</v>
+        <v>-1.4582</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-2.3113</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.4056</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.9057</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1377</v>
+        <v>-1.5535</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1381</v>
+        <v>-2.001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2758</v>
+        <v>0.4475</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9308</v>
+        <v>3.6685</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.6685</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0607</v>
+        <v>-1.7241</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0275</v>
+        <v>-1.435</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0882</v>
+        <v>-0.2892</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2277</v>
+        <v>-0.451</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-2.5781</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1576</v>
+        <v>-2.9035</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0328</v>
+        <v>-1.7998</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1248</v>
+        <v>-1.1037</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8648</v>
+        <v>0.1377</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4066</v>
+        <v>-0.1381</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4582</v>
+        <v>0.2758</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3113</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4056</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9057</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5535</v>
+        <v>0.1377</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.001</v>
+        <v>-0.1381</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4475</v>
+        <v>0.2758</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6685</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6685</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5103</v>
+        <v>0.1172</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8487</v>
+        <v>0.131</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6617</v>
+        <v>-0.0137</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.451</v>
+        <v>-1.2277</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1271</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5781</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5309</v>
+        <v>-3.5764</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4125</v>
+        <v>-3.3091</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1183</v>
+        <v>-0.2673</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6093</v>
@@ -1390,13 +1390,13 @@
         <v>2.3169</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3201</v>
+        <v>-0.3656</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4142</v>
+        <v>-0.3107</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0941</v>
+        <v>-0.0549</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0222</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.4047</v>
+        <v>-14.4048</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.2714</v>
+        <v>-17.2713</v>
       </c>
       <c r="F13" t="n">
-        <v>2.866899999999999</v>
+        <v>2.8667</v>
       </c>
       <c r="G13" t="n">
         <v>-16.2064</v>
@@ -1438,7 +1438,7 @@
         <v>-16.2064</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="J13" t="n">
         <v>-6.748</v>
@@ -1456,7 +1456,7 @@
         <v>-13.1089</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6504</v>
+        <v>3.650399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>6.7577</v>
@@ -1468,13 +1468,13 @@
         <v>19.3077</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.2418</v>
+        <v>-5.241699999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-4.5552</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6865</v>
+        <v>-0.6864000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.2854999999999996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4597</v>
+        <v>6.6502</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4571</v>
+        <v>2.7331</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0026</v>
+        <v>3.917</v>
       </c>
       <c r="G14" t="n">
         <v>4.1828</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3888</v>
+        <v>1.5792</v>
       </c>
       <c r="T14" t="n">
-        <v>1.02</v>
+        <v>0.296</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3688</v>
+        <v>1.2832</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7164</v>
+        <v>5.5055</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9883</v>
+        <v>2.678</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7282</v>
+        <v>2.8275</v>
       </c>
       <c r="G15" t="n">
         <v>7.4626</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5281</v>
+        <v>1.3172</v>
       </c>
       <c r="T15" t="n">
-        <v>0.496</v>
+        <v>0.1858</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0321</v>
+        <v>1.1314</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5712</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8903</v>
+        <v>4.8059</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0515</v>
+        <v>0.8789</v>
       </c>
       <c r="F16" t="n">
-        <v>3.8388</v>
+        <v>3.927</v>
       </c>
       <c r="G16" t="n">
         <v>4.5256</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4189</v>
+        <v>0.4967</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9381</v>
+        <v>-0.1107</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5192</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.9421</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2635</v>
+        <v>2.8182</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7981</v>
+        <v>0.8673</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4654</v>
+        <v>1.9509</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2233</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8383</v>
+        <v>0.393</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5718</v>
+        <v>0.641</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7335</v>
+        <v>-0.248</v>
       </c>
       <c r="V17" t="n">
         <v>2.4554</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0975</v>
+        <v>0.198</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8</v>
+        <v>-1.7185</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7025</v>
+        <v>1.9164</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6562</v>
+        <v>0.4114</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1033</v>
+        <v>1.1032</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7595</v>
+        <v>-0.6918</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7861</v>
+        <v>0.1916</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8617</v>
+        <v>1.4485</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9245</v>
+        <v>-1.2569</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1299</v>
+        <v>0.2198</v>
       </c>
       <c r="N18" t="n">
-        <v>0.965</v>
+        <v>-0.3453</v>
       </c>
       <c r="O18" t="n">
-        <v>0.165</v>
+        <v>0.5651</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6513</v>
+        <v>0.4897</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.2416</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7343</v>
+        <v>0.7312</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
         <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1371</v>
+        <v>-0.1004</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0287</v>
+        <v>-1.5931</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8916</v>
+        <v>1.4928</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4114</v>
+        <v>-0.6562</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1032</v>
+        <v>0.1033</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6918</v>
+        <v>-0.7595</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1916</v>
+        <v>-1.7861</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4485</v>
+        <v>-0.8617</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2569</v>
+        <v>-0.9245</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2198</v>
+        <v>1.1299</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3453</v>
+        <v>0.965</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5651</v>
+        <v>0.165</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8962</v>
+        <v>-1.1585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1546</v>
+        <v>0.6484</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5518</v>
+        <v>0.1238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7064</v>
+        <v>0.5246</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W19" t="n">
         <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8445</v>
+        <v>-0.2929</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9878</v>
+        <v>-1.5741</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1433</v>
+        <v>1.2812</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8582</v>
@@ -2014,13 +2014,13 @@
         <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>0.083</v>
+        <v>0.6345</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4693</v>
+        <v>-0.0557</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5523</v>
+        <v>0.6902</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0995</v>
+        <v>-0.6402</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9774</v>
+        <v>-0.6671</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1221</v>
+        <v>0.0269</v>
       </c>
       <c r="G21" t="n">
         <v>0.1047</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2041</v>
+        <v>0.2551</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4415</v>
+        <v>-0.1312</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2373</v>
+        <v>0.3863</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3938</v>
+        <v>-1.5261</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5367</v>
+        <v>-1.7436</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1429</v>
+        <v>0.2174</v>
       </c>
       <c r="G22" t="n">
         <v>1.868</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1324</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3584</v>
+        <v>0.1515</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.226</v>
+        <v>-0.1515</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2703</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3529</v>
+        <v>-2.324</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8311</v>
+        <v>-2.7277</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4782</v>
+        <v>0.4037</v>
       </c>
       <c r="G23" t="n">
         <v>-0.611</v>
@@ -2248,13 +2248,13 @@
         <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1173</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3643</v>
+        <v>0.2898</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.4046</v>
+        <v>15.0942</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.866700000000001</v>
+        <v>-2.8668</v>
       </c>
       <c r="F24" t="n">
-        <v>17.2714</v>
+        <v>17.9608</v>
       </c>
       <c r="G24" t="n">
         <v>16.2064</v>
@@ -2326,13 +2326,13 @@
         <v>12.55</v>
       </c>
       <c r="S24" t="n">
-        <v>5.2419</v>
+        <v>5.931100000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6865000000000001</v>
+        <v>0.6864</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5552</v>
+        <v>5.244599999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2855</v>
